--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Llama-3.3-70B-Instruct/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.3703703703703703</v>
+        <v>0.2666666666666667</v>
       </c>
       <c r="B2">
-        <v>0.01818181818181818</v>
+        <v>0.01639344262295082</v>
       </c>
       <c r="C2">
-        <v>0.3802816901408451</v>
+        <v>0.3450704225352113</v>
       </c>
       <c r="D2">
-        <v>0.8073394495412844</v>
+        <v>0.8773584905660378</v>
       </c>
       <c r="E2">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F2">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="G2">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
